--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40727-2026 artfynd.xlsx
+++ b/artfynd/A 40727-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136648859</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136648866</v>
       </c>
       <c r="B3" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136648867</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136648858</v>
       </c>
       <c r="B5" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
